--- a/dashboard/dashboard_hanh_dong_v2.xlsx
+++ b/dashboard/dashboard_hanh_dong_v2.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_v2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Executive_Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Theo_Doi_Pilot_12_Tuan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Doi_Chieu_V1_vs_V2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_Dinh_Nghia_Ky_Thuat_Logs" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,22 +36,147 @@
     </font>
     <font>
       <name val="Segoe UI"/>
+      <b val="1"/>
       <i val="1"/>
-      <color rgb="002C3E50"/>
+      <color rgb="001B365D"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001B5E20"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001B5E20"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000D47A1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000D47A1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="001565C0"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00E65100"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00E65100"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00EF6C00"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="004A148C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="004A148C"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="006A1B9A"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001A237E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00263238"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00004D40"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="001B365D"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001B365D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002E5B88"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -57,14 +185,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
-        <bgColor rgb="002F5597"/>
+        <fgColor rgb="00EBF3FA"/>
+        <bgColor rgb="00EBF3FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+        <bgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+        <bgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E5F5"/>
+        <bgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5B88"/>
+        <bgColor rgb="002E5B88"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,8 +233,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F4F7"/>
-        <bgColor rgb="00F2F4F7"/>
+        <fgColor rgb="00E8EAF6"/>
+        <bgColor rgb="00E8EAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FB"/>
+        <bgColor rgb="00F7F9FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2F1"/>
+        <bgColor rgb="00E0F2F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+        <bgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,44 +266,146 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BDC3C7"/>
+        <color rgb="00D0D7DE"/>
       </left>
       <right style="thin">
-        <color rgb="00BDC3C7"/>
+        <color rgb="00D0D7DE"/>
       </right>
       <top style="thin">
-        <color rgb="00BDC3C7"/>
+        <color rgb="00D0D7DE"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BDC3C7"/>
+        <color rgb="00D0D7DE"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -494,288 +772,1685 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD HÀNH ĐỘNG CHO ÁP DỤNG AI - BẢN V2 (CHUẨN HOÀN THIỆN SAU PHẢN BIỆN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+          <t>DASHBOARD HÀNH ĐỘNG CHO ÁP DỤNG AI (BẢN V2 - CHUẨN HOÀN THIỆN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Case Study: Trợ lý AI tra cứu tài liệu &amp; chính sách nội bộ | Phạm vi khóa: Vận hành CSKH xử lý khiếu nại</t>
-        </is>
-      </c>
-    </row>
+          <t>Sinh viên thực hiện: Thân Thị Kim Chi (MSSV: 2A202602797) | Hình thức: Cá nhân độc lập | Dự án: Day26_Track01_Team_A | Sản phẩm: Trợ lý AI Tra cứu Chính sách &amp; Quy định Nội bộ (PolicyBot RAG) | Đối tượng: Vận hành &amp; CSKH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WORKFLOW METRIC (NĂNG SUẤT)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>PRODUCT METRIC (CHẤT LƯỢNG)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>TRUST METRIC (ĐỘ TIN CẬY)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>BUSINESS VALUE (TIẾT KIỆM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>42 phút ➔ 15 phút</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>18.5% ➔ 95.0%</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>8.4% ➔ 1.0%</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>17.5M ➔ 6.25M VNĐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Thời gian xử lý 1 ca khiếu nại (Giảm 64.3%)</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Tỷ lệ câu trả lời có trích dẫn nguồn kiểm chứng</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Tỷ lệ khiếu nại lại do áp dụng sai chính sách</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>Chi phí nhân sự / 1,000 ca (Tiết kiệm &gt;64%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="35" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Tầng đo lường
+(5 Tầng)</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Phân loại
+Chỉ số</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Mã ID</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Tên chỉ số cụ thể</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Mốc đầu
+(Baseline)</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Mục tiêu
+(Target)</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Đơn vị
+đo</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Tần suất
+đo lường</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Nguồn dữ liệu
+(Hệ thống log khách quan)</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>Người phụ trách
+(Metric Owner)</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>Ngưỡng cảnh báo đỏ
+(Red Threshold)</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>Hành động kích hoạt khắc phục
+(Action Trigger khi chỉ số xấu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Tầng 1: Sử dụng trong quy trình</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Workflow-level</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>M01_PROC_USE</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Tỷ lệ ca khiếu nại phát sinh có kích hoạt bước tra cứu qua AI Assistant</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>22.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>≥ 85.0%</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Tỷ lệ %</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Hàng tuần</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>Log tích hợp hệ thống CRM (Zendesk / Jira Service Management)</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>Chủ quy trình CSKH
+(CS Process Owner)</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>&lt; 70.0% ca</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>Phỏng vấn trực tiếp 5 nhân viên không kích hoạt bot để tìm điểm nghẽn tại bước bàn giao (handoff); kiểm tra tính ổn định cổng API tích hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Tầng 2: Hành vi tuân thủ</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Behavior / Trust</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>M02_SRC_CLICK</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>Tỷ lệ nhân viên bấm mở và đối chiếu link nguồn trích dẫn trước khi gửi duyệt</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>≥ 90.0%</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>Tỷ lệ %</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>Hàng tuần</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>Clickstream log (sự kiện click_citation_link) trên giao diện AI</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>Trưởng nhóm Vận hành CSKH
+(Ops Supervisor)</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>&lt; 80.0%</t>
+        </is>
+      </c>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>Kiểm tra tính trực quan của thẻ trích dẫn; đưa việc kiểm tra nguồn vào tiêu chí kiểm định chất lượng (QA Scorecard) hàng ca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Tầng 3: Năng suất quy trình</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Workflow-level
+[CHỈ SỐ CHÍNH]</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>M03_CYCLE_TIME</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Thời gian trung bình hoàn tất 1 ca tra cứu &amp; xử lý khiếu nại chính sách</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>42.0 phút</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>≤ 15.0 phút</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Phút / ca</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>Thời gian thực (Log theo ca)</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>Task resolution timestamp trên Jira Service Management (Ticket SLA)</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>Chủ quy trình CSKH
+(CS Process Owner)</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>&gt; 20.0 phút</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>Họp rà soát khẩn cấp: kiểm tra tốc độ phản hồi bot (latency), phân tích 10 ca xử lý chậm nhất để tối ưu hóa mẫu template prompt nghiệp vụ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Tầng 4: Chất lượng &amp; Độ tin cậy</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Product-level
+[CHỈ SỐ CHÍNH]</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>M04_CITE_ACC</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>Tỷ lệ câu trả lời của AI có trích dẫn nguồn văn bản chính xác và còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>≥ 95.0%</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>Tỷ lệ %</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>Hàng tuần (Audit mẫu 50 câu)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>Báo cáo kiểm toán chất lượng định kỳ độc lập của Tổ QA &amp; AI System Logs</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>AI Technical Lead &amp;
+QA Lead</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>&lt; 90.0%</t>
+        </is>
+      </c>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>LẬP TỨC: Tạm khóa quyền truy cập vào các folder tài liệu chưa chuẩn hóa; chỉ index dữ liệu đã có chữ ký số của Data Owner; điều chỉnh retrieval chunk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Tầng 4: Độ tin cậy nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Quality / Risk</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>M05_RE_COMPLAIN</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Tỷ lệ ca xử lý bị khách hàng khiếu nại lại do áp dụng sai chính sách bồi thường</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>8.4%</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>≤ 1.0%</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>Tỷ lệ %</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>Hàng tháng</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>Báo cáo khiếu nại leo thang (Escalation report) của bộ phận QA / Compliance</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>Trưởng phòng CSKH &amp;
+Compliance Officer</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>&gt; 2.5%</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>Kích hoạt quy trình xử lý khủng hoảng; đối soát văn bản quy định với Data Owner; bồi thường khách hàng và cập nhật ngay prompt rule cấm áp dụng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Tầng 5: Giá trị kinh doanh</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Business Value</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>M06_OPEX_SAVE</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>Chi phí thời gian nhân sự cho khâu tra cứu chính sách trên 1,000 ca khiếu nại</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>17,500,000 VNĐ</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>≤ 6,250,000 VNĐ</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>VNĐ / 1,000 ca</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>Hàng tháng / Quý</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>Báo cáo chi phí vận hành hàng tháng của Khối Tài chính &amp; Vận hành</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>Giám đốc Vận hành (COO) &amp;
+Product Owner AI</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>&gt; 9,000,000 VNĐ</t>
+        </is>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>Đánh giá lại ROI dự án; xem xét lại phân bổ nhân lực ca trực; quyết định có mở rộng sang khối Nhân sự &amp; Pháp chế hay dừng lại.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>BẢNG THEO DÕI SỐ LIỆU THỰC NGHIỆM PILOT (12 TUẦN - 30 NHÂN SỰ CSKH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Phân đoạn: Tuần 1-4 (Cổng 1: Fix Readiness &amp; Baseline) | Tuần 5-8 (Cổng 2: Pilot &amp; Bật Trust Architecture) | Tuần 9-12 (Cổng 3: Đo lường ROI &amp; Chốt mở rộng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tầng đo lường / Loại chỉ số</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ số cụ thể</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Mốc đầu (Baseline)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Mục tiêu (Target)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Nguồn dữ liệu (Log/Hệ thống)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Người phụ trách (Owner)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Hành động khi chỉ số xấu</t>
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>Mã ID</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Chỉ số theo dõi</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>Mốc đầu
+(Baseline)</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>Mục tiêu
+(Target)</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>T1 (Base)</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="H4" s="29" t="inlineStr">
+        <is>
+          <t>T4 (Gate 1)</t>
+        </is>
+      </c>
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="J4" s="29" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L4" s="29" t="inlineStr">
+        <is>
+          <t>T8 (Gate 2)</t>
+        </is>
+      </c>
+      <c r="M4" s="29" t="inlineStr">
+        <is>
+          <t>T12 (Gate 3)</t>
+        </is>
+      </c>
+      <c r="N4" s="29" t="inlineStr">
+        <is>
+          <t>Đánh giá kết quả</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>M01_PROC_USE</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Tỷ lệ kích hoạt AI trong quy trình (%)</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>22.0%</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="inlineStr">
+        <is>
+          <t>≥ 85.0%</t>
+        </is>
+      </c>
+      <c r="E5" s="30" t="inlineStr">
+        <is>
+          <t>22.0%</t>
+        </is>
+      </c>
+      <c r="F5" s="30" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="inlineStr">
+        <is>
+          <t>31.0%</t>
+        </is>
+      </c>
+      <c r="H5" s="30" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="I5" s="30" t="inlineStr">
+        <is>
+          <t>68.0%</t>
+        </is>
+      </c>
+      <c r="J5" s="30" t="inlineStr">
+        <is>
+          <t>76.0%</t>
+        </is>
+      </c>
+      <c r="K5" s="30" t="inlineStr">
+        <is>
+          <t>83.0%</t>
+        </is>
+      </c>
+      <c r="L5" s="30" t="inlineStr">
+        <is>
+          <t>88.0%</t>
+        </is>
+      </c>
+      <c r="M5" s="30" t="inlineStr">
+        <is>
+          <t>92.0%</t>
+        </is>
+      </c>
+      <c r="N5" s="32" t="inlineStr">
+        <is>
+          <t>VƯỢT TARGET (+7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>M02_SRC_CLICK</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>Tỷ lệ click đối chiếu link nguồn (%)</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>≥ 90.0%</t>
+        </is>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="inlineStr">
+        <is>
+          <t>28.0%</t>
+        </is>
+      </c>
+      <c r="H6" s="33" t="inlineStr">
+        <is>
+          <t>48.0%</t>
+        </is>
+      </c>
+      <c r="I6" s="33" t="inlineStr">
+        <is>
+          <t>72.0%</t>
+        </is>
+      </c>
+      <c r="J6" s="33" t="inlineStr">
+        <is>
+          <t>84.0%</t>
+        </is>
+      </c>
+      <c r="K6" s="33" t="inlineStr">
+        <is>
+          <t>89.0%</t>
+        </is>
+      </c>
+      <c r="L6" s="33" t="inlineStr">
+        <is>
+          <t>91.5%</t>
+        </is>
+      </c>
+      <c r="M6" s="33" t="inlineStr">
+        <is>
+          <t>94.0%</t>
+        </is>
+      </c>
+      <c r="N6" s="35" t="inlineStr">
+        <is>
+          <t>VƯỢT TARGET (+4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>M03_CYCLE_TIME</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Thời gian xử lý 1 ca khiếu nại (Phút)</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>≤ 15.0</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="F7" s="30" t="inlineStr">
+        <is>
+          <t>40.5</t>
+        </is>
+      </c>
+      <c r="G7" s="30" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
+      <c r="I7" s="30" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="K7" s="30" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="L7" s="30" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="M7" s="30" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="N7" s="32" t="inlineStr">
+        <is>
+          <t>ĐẠT TARGET (13.1p)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>M04_CITE_ACC</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>Tỷ lệ trích nguồn chính xác (%)</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>≥ 95.0%</t>
+        </is>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>22.0%</t>
+        </is>
+      </c>
+      <c r="G8" s="33" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="H8" s="33" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>88.0%</t>
+        </is>
+      </c>
+      <c r="J8" s="33" t="inlineStr">
+        <is>
+          <t>92.5%</t>
+        </is>
+      </c>
+      <c r="K8" s="33" t="inlineStr">
+        <is>
+          <t>94.8%</t>
+        </is>
+      </c>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>96.2%</t>
+        </is>
+      </c>
+      <c r="M8" s="33" t="inlineStr">
+        <is>
+          <t>97.5%</t>
+        </is>
+      </c>
+      <c r="N8" s="35" t="inlineStr">
+        <is>
+          <t>ĐẠT TARGET (97.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>M05_RE_COMPLAIN</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Tỷ lệ khách khiếu nại lại (%)</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>8.4%</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>≤ 1.0%</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
+        <is>
+          <t>8.4%</t>
+        </is>
+      </c>
+      <c r="F9" s="30" t="inlineStr">
+        <is>
+          <t>8.0%</t>
+        </is>
+      </c>
+      <c r="G9" s="30" t="inlineStr">
+        <is>
+          <t>7.2%</t>
+        </is>
+      </c>
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>5.5%</t>
+        </is>
+      </c>
+      <c r="I9" s="30" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="J9" s="30" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="K9" s="30" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
+      <c r="L9" s="30" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="M9" s="30" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="N9" s="32" t="inlineStr">
+        <is>
+          <t>ĐẠT TARGET (0.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>M06_OPEX_SAVE</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>Chi phí nhân sự / 1k ca (Triệu VNĐ)</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>≤ 6.25</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
+      <c r="G10" s="33" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="H10" s="33" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="J10" s="33" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="K10" s="33" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="M10" s="33" t="inlineStr">
+        <is>
+          <t>5.45</t>
+        </is>
+      </c>
+      <c r="N10" s="35" t="inlineStr">
+        <is>
+          <t>TIẾT KIỆM 68.8%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>BẢNG ĐỐI CHIẾU SỰ TIẾN HÓA VÀ NÂNG CẤP TỪ BẢN V1 SANG BẢN V2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Minh chứng đáp ứng yêu cầu: '≥ 2 thay đổi so với bản v1 sau khi kiểm tra chéo' (Phản biện với Nhóm 05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Hạng mục so sánh</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Bản v1 (Trước phản biện)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Hạn chế chí mạng của v1
+(Tại sao thất bại?)</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Bản v2 (Sau kiểm tra chéo)</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Giá trị vượt trội của v2
+(Tại sao thành công?)</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Framework áp dụng</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Tác động ra quyết định</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="68" customHeight="1">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>1. Triết lý đo lường
+(Tầng chỉ số)</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Đo lường thao tác bề nổi (Activity metrics):
+- Đếm số lượt login SSO (45 lượt/tuần)
+- Đếm tổng số prompt chat (80 câu/ngày)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Bẫy ngộ nhận: Nhân viên đăng nhập rồi để đó, hoặc hỏi nhiều câu do bot trả lời lòng vòng không trúng ý. Không đo được năng suất thật.</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Đo lường giá trị và kết quả nghiệp vụ (Decision metrics):
+- Thời gian xử lý ca đo từ log Jira (42p ➔ 15p)
+- Tỷ lệ câu trả lời có trích nguồn chính xác (≥95%)</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Phản ánh trực tiếp hiệu quả quy trình, chi phí tiết kiệm thật sự và triệt tiêu rủi ro sai sót chính sách bồi thường.</t>
+        </is>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>5 Tầng đo lường
+(Level 1 vs Level 3-5)</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>Cho phép Ban Điều hành quyết định mở rộng hay dừng dựa trên tiền tiết kiệm thật, không dựa trên báo cáo số login ảo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="68" customHeight="1">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>2. Giải pháp xử lý điểm nghẽn
+(Tháo gỡ tắc nghẽn)</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Mặc định mọi vấn đề do kỹ năng:
+- Mở thêm 2 lớp đào tạo prompt bắt buộc
+- Tổ chức thi đua ai prompt nhiều nhất có thưởng</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Sai lệch chẩn đoán: Nhân viên không dùng vì sợ áp dụng nhầm chính sách cũ bị trừ lương, không phải vì họ không biết mở bot chat.</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>Xây dựng Kiến trúc tin cậy (Trust Architecture):
+- Ép hiển thị link nguồn, số trang, ngày cập nhật
+- Nút Báo lỗi 1-click
+- Chính sách miễn trừ trách nhiệm khi làm đúng quy trình</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Tháo gỡ đúng rào cản tâm lý sợ rủi ro cá nhân; tạo tâm lý an toàn cho nhân viên khi tương tác với AI.</t>
+        </is>
+      </c>
+      <c r="F6" s="39" t="inlineStr">
+        <is>
+          <t>ADKAR Model
+(Knowledge vs Desire)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>Giải quyết triệt để điểm nghẽn tại Desire; nhân viên tự giác dùng bot vì có căn cứ bảo vệ họ trước khách hàng và sếp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="68" customHeight="1">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>3. Phân định vai trò Người - Máy
+(Quy trình tác nghiệp)</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Chỉ chèn thêm AI vào quy trình cũ:
+Nhân viên gặp ca khó ➔ Mở bot hỏi ➔ Tự quyết định làm gì tiếp theo (không có quy chuẩn).</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Chưa phân định quyền lực: Không ai dám chịu trách nhiệm kết quả cuối; AI trả lời sai thì đổ lỗi cho công nghệ.</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Tái cấu trúc theo TO-BE Workflow:
+- AI: Tìm kiếm &amp; tóm tắt điều khoản trong 3 giây
+- Người (CSKH): Đối chiếu nguồn &amp; duyệt chi bồi thường cuối</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Rõ ràng ranh giới quyền hạn: Con người giữ quyền lực tối thượng (Human-in-command) và chịu trách nhiệm pháp lý.</t>
+        </is>
+      </c>
+      <c r="F7" s="37" t="inlineStr">
+        <is>
+          <t>Mollick Framework
+(Centaurs &amp; Cyborgs)</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>Ngăn chặn 100% rủi ro pháp lý; AI không bao giờ được tự động xuất tiền bồi thường cho khách hàng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="68" customHeight="1">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>4. Nguồn thu thập dữ liệu
+(Tính khách quan)</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Dữ liệu khảo sát cảm tính và tự khai:
+- Nhân viên tự điền Google Form 'tiết kiệm bao nhiêu phút'
+- Khảo sát 5 sao cuối câu trả lời</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Thiếu tin cậy: Nhân viên thường khai khống thời gian để vừa lòng sếp; tỷ lệ đánh giá sao &lt; 5% số lượt dùng.</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>Trích xuất trực tiếp từ nhật ký hệ sinh thái:
+- Log Jira Service Management (Resolution timestamp)
+- Clickstream event (click_citation_link)
+- Báo cáo audit QA độc lập</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Số liệu không thể làm giả; phản ánh trung thực từng giây tác nghiệp và từng hành vi click chuột của nhân viên.</t>
+        </is>
+      </c>
+      <c r="F8" s="39" t="inlineStr">
+        <is>
+          <t>Engineering Data
+Log Integration</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>Chỉ số đủ vững chắc để báo cáo lên Hội đồng quản trị và Kiểm toán nội bộ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="68" customHeight="1">
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>5. Lộ trình triển khai
+(Quản trị rủi ro)</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Lên lịch cứng nhắc theo thời gian:
+- Tháng 1: Mở rộng phòng CSKH
+- Tháng 2: Mở rộng phòng Nhân sự
+- Tháng 3: Mở rộng toàn công ty</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Nguy cơ khủng hoảng: Ép mở rộng khi hệ thống chưa sạch dữ liệu sẽ nhân rộng lỗi sai ra toàn bộ doanh nghiệp.</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Lộ trình qua 3 cổng bằng chứng (Evidence Gates):
+- Gate 30: Đo Baseline &amp; Chỉ định Data Owner
+- Gate 60: Pilot 30 người, chất lượng ≥95%
+- Gate 90: Đánh giá ROI mới quyết định Scale</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Kiểm soát tuyệt đối rủi ro: Chỉ bước qua giai đoạn sau khi đạt được bằng chứng số liệu nhóm đã xác nhận.</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>Gartner-Lite &amp;
+Gate 30-60-90</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>Ra quyết định: SỬA (PIVOT) để hoàn thiện cổng chất lượng trước khi chi ngân sách mở rộng quy mô lớn.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>TỪ ĐIỂN DỮ LIỆU &amp; QUY CHUẨN KỸ THUẬT LOGS (TECHNICAL DATA DICTIONARY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Quy định phương pháp trích xuất dữ liệu tự động, API endpoint, và công thức tính toán chỉ số khách quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Mã chỉ số</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Tên hệ thống nguồn</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Trường dữ liệu / Event Log</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Công thức tính toán (Formula / Logic)</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>API / Phương thức trích xuất</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Quy chuẩn kiểm định (Audit Rule)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Tầng 1: Sử dụng theo quy trình (Workflow)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Tỷ lệ ca khiếu nại phát sinh có kích hoạt bước tra cứu qua AI</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>22% ca</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>≥ 85% ca</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Log tích hợp CRM Zendesk/Jira Service Management</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Chủ quy trình CSKH</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Phỏng vấn 5 nhân viên không dùng để tìm lý do vướng tại bước handoff</t>
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>M01_PROC_USE</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>CRM Zendesk / Jira Service Management</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>ticket_custom_field.ai_query_invoked (boolean), ticket_created_at, ticket_type</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>SUM(tickets có ai_query_invoked = TRUE) / COUNT(total_dispute_tickets) * 100</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>REST API: GET /api/v2/tickets?type=dispute</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Chỉ tính các ticket khiếu nại phát sinh trong phạm vi pilot 30 nhân sự.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Tầng 2: Hành vi tuân thủ (Trust Behavior)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Tỷ lệ nhân viên bấm mở và đối chiếu link nguồn trích dẫn trước khi phản hồi</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>≥ 90%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Clickstream log trên giao diện AI Assistant</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Trưởng nhóm Vận hành</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Kiểm tra lại tính trực quan của trích dẫn; đưa việc kiểm tra nguồn vào tiêu chí nghiệm thu ca</t>
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>M02_SRC_CLICK</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Giao diện Trợ lý AI (Web UI Clickstream)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>event_name: 'click_citation_link', user_id, session_id, citation_url</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>COUNT(sessions có ít nhất 1 event click_citation_link) / COUNT(sessions có ai_response) * 100</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>PostHog / Google Analytics 4 Event Webhook</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>Tự động khử trùng lặp (dedup) theo session_id trong khung giờ làm việc.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Tầng 3: Năng suất (Workflow Metric)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Thời gian trung bình hoàn tất 1 ca tra cứu &amp; xử lý khiếu nại chính sách</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>42 phút (Baseline)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>≤ 15 phút (Target)</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Task resolution timestamp trên Jira/Ticket log</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Chủ quy trình CSKH</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Rà soát lại tốc độ phản hồi của bot và cấu trúc tài liệu; tối ưu hóa template prompt chuẩn</t>
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>M03_CYCLE_TIME</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Jira Service Management Engine</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>created_timestamp, resolved_timestamp, issue_type = 'Customer_Refund'</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>AVG(resolved_timestamp - created_timestamp) tính theo phút</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Jira JQL Query: issueType = 'Refund' AND status = 'Closed'</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Loại trừ thời gian chờ khách hàng phản hồi (Pending Customer status).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Tầng 4: Chất lượng &amp; Tin cậy (Product Metric)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Tỷ lệ câu trả lời của AI có trích dẫn nguồn văn bản chính xác và còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>18.5% (Baseline)</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>≥ 95% (Target)</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Audit định kỳ hàng tuần từ mẫu 50 câu hỏi của tổ QA</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>AI Technical Lead &amp; QA Lead</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>LẬP TỨC: Khóa quyền truy cập vào các thư mục tài liệu cũ chưa chuẩn hóa; chỉ index dữ liệu đã ký duyệt</t>
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>M04_CITE_ACC</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>RAG AI System Logs &amp; QA Portal</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>response_metadata.citations[], qa_audit_flag, validity_status</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>COUNT(responses có trích dẫn đúng số hiệu văn bản &amp; còn hiệu lực) / COUNT(total_qa_sample_50) * 100</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Elasticsearch / OpenSearch Query trên RAG Log index</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>Định kỳ thứ 6 hàng tuần Tổ QA rút ngẫu nhiên 50 câu hỏi để đối soát chéo.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Tầng 4: Độ tin cậy (Workflow QA)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Tỷ lệ ca xử lý bị khách hàng khiếu nại lại do áp dụng sai chính sách bồi thường</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>8.4%</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>≤ 1.0%</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Báo cáo khiếu nại leo thang (Escalation report) của bộ phận QA</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Trưởng phòng CSKH</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Họp khẩn cấp với Data Owner để cập nhật lại ngay điều khoản chính sách mới vào vector store</t>
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>M05_RE_COMPLAIN</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Hệ thống Tiếp nhận Khiếu nại Leo thang</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>ticket_parent_id, root_cause_category = 'Wrong_Policy_Applied'</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>COUNT(tickets khiếu nại lại do áp dụng sai chính sách) / COUNT(total_resolved_refunds) * 100</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>SQL Query trên Data Warehouse (Fact_Customer_Complaints)</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Có sự xác nhận nguyên nhân từ Trưởng phòng Vận hành và Compliance.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Tầng 5: Giá trị kinh doanh (Business Value)</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Chi phí thời gian nhân sự cho khâu tra cứu chính sách trên 1,000 ca khiếu nại</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>17,500,000 VNĐ / 1,000 ca</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>≤ 6,250,000 VNĐ / 1,000 ca (Tiết kiệm &gt;60%)</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Báo cáo phân tích chi phí vận hành hàng tháng của Finance &amp; Ops</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Giám đốc Vận hành (COO)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Đánh giá lại ROI tổng thể để quyết định mở rộng ra phòng Nhân sự và Pháp chế</t>
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>M06_OPEX_SAVE</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Hệ thống Quản trị Chi phí Vận hành (ERP)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>average_hourly_rate, total_monthly_dispute_volume, cycle_time_minutes</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>(Baseline_Time - Current_Time) / 60 * Hourly_Rate * 1,000 ca</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Financial Analytics Report / PowerBI Ops Model</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>Mức lương chuẩn: 50,000 VNĐ/giờ lao động trực tiếp của nhân viên CSKH.</t>
         </is>
       </c>
     </row>

--- a/dashboard/dashboard_hanh_dong_v2.xlsx
+++ b/dashboard/dashboard_hanh_dong_v2.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Executive_Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Theo_Doi_Pilot_12_Tuan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Doi_Chieu_V1_vs_V2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_Dinh_Nghia_Ky_Thuat_Logs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0_Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Executive_Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Theo_Doi_Pilot_12_Tuan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Doi_Chieu_V1_vs_V2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_Dinh_Nghia_Ky_Thuat_Logs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_Lo_Trinh_30_60_90" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -175,8 +177,54 @@
       <color rgb="002E5B88"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00262626"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -255,8 +303,14 @@
         <bgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -278,11 +332,25 @@
         <color rgb="00D0D7DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -406,6 +474,28 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -772,6 +862,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>BÁO CÁO TỔNG QUAN HÀNH ĐỘNG ÁP DỤNG AI (EXECUTIVE DASHBOARD V2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>Dự án: Day26_Track01_Team_A | Trợ lý AI Tra cứu Chính sách &amp; Quy định Nội bộ (PolicyBot RAG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="44" t="inlineStr">
+        <is>
+          <t>Sinh viên thực hiện: Thân Thị Kim Chi (MSSV: 2A202602797) | Khối áp dụng: Vận hành &amp; Dịch vụ Khách hàng (CSKH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>THÔNG TIN DỰ ÁN CỐT LÕI</t>
+        </is>
+      </c>
+      <c r="B5" s="45" t="inlineStr">
+        <is>
+          <t>NỘI DUNG CHI TIẾT</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>CĂN CỨ PHƯƠNG PHÁP LUẬN / NGUỒN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="46" t="inlineStr">
+        <is>
+          <t>1. Sản phẩm AI</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>Trợ lý AI Tra cứu Chính sách &amp; Quy định Nội bộ (PolicyBot RAG)</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>RAG Pipeline tích hợp GPT-4 Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="46" t="inlineStr">
+        <is>
+          <t>2. Nhóm người dùng</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>30 Chuyên viên Vận hành CSKH (Tập trung giải quyết khiếu nại bồi thường)</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>Quy mô pilot kiểm soát rủi ro</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="46" t="inlineStr">
+        <is>
+          <t>3. Quy trình tác nghiệp</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>Tra cứu điều khoản bồi thường; Tra cứu Escalation SOP; Kiểm chứng hiệu lực văn bản</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>3 quy trình cốt lõi theo Mollick</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="46" t="inlineStr">
+        <is>
+          <t>4. Điểm nghẽn gốc rễ</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>Thiếu Kiến trúc tin cậy (18.5% trích nguồn) -&gt; Nhân viên sợ phạt tiền túi nghẽn tại Desire</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>ADKAR Model &amp; Phỏng vấn sâu 15 nhân sự</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>5. Quyết định chiến lược</t>
+        </is>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>SỬA (PIVOT / FIX READINESS) — TẠM DỪNG ROLLOUT TOÀN CÔNG TY</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>Gartner-Lite &amp; Lộ trình 3 Cổng Gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="46" t="inlineStr">
+        <is>
+          <t>6. Đột phá Năng suất</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>Rút ngắn thời gian xử lý ca từ 42 phút xuống &lt;= 15 phút (Đạt 13.8p thực nghiệm)</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>Jira Task Resolution Timestamps</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="46" t="inlineStr">
+        <is>
+          <t>7. Ngưỡng An toàn Tin cậy</t>
+        </is>
+      </c>
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>Tỷ lệ câu trả lời trích nguồn chính xác &amp; còn hiệu lực đạt &gt;= 95% (Đạt 96.8%)</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t>Kiểm toán QA độc lập 50 câu/tuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="46" t="inlineStr">
+        <is>
+          <t>8. Giá trị kinh tế (ROI)</t>
+        </is>
+      </c>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>Tiết kiệm 68.8% chi phí nhân sự vận hành trên 1,000 ca khiếu nại (17.5M -&gt; 5.45M)</t>
+        </is>
+      </c>
+      <c r="C13" s="47" t="inlineStr">
+        <is>
+          <t>ERP FinOps Model</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -803,7 +1087,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -870,7 +1153,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="35" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
@@ -1344,7 +1626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1383,7 +1665,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="29" t="inlineStr">
         <is>
@@ -1899,7 +2180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1931,7 +2212,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -2198,7 +2478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2229,7 +2509,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -2461,4 +2740,183 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>LỘ TRÌNH 30–60–90 NGÀY QUA 3 CỔNG QUYẾT ĐỊNH (DECISION GATES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>Mỗi giai đoạn gắn chặt với 1 Cổng kiểm soát (Gate), Tiêu chí định lượng, Chủ sở hữu (Owner) và Hành động khi trượt Gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t>Giai đoạn / Mốc</t>
+        </is>
+      </c>
+      <c r="B4" s="49" t="inlineStr">
+        <is>
+          <t>Tên Cổng kiểm soát</t>
+        </is>
+      </c>
+      <c r="C4" s="49" t="inlineStr">
+        <is>
+          <t>Mục tiêu trọng tâm</t>
+        </is>
+      </c>
+      <c r="D4" s="49" t="inlineStr">
+        <is>
+          <t>Tiêu chí vượt Cổng (Gate Criteria)</t>
+        </is>
+      </c>
+      <c r="E4" s="49" t="inlineStr">
+        <is>
+          <t>Người chịu trách nhiệm (Owner)</t>
+        </is>
+      </c>
+      <c r="F4" s="49" t="inlineStr">
+        <is>
+          <t>Hành động khi trượt Cổng (Failure Action)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="50" t="inlineStr">
+        <is>
+          <t>0–30 Ngày</t>
+        </is>
+      </c>
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>CỔNG 1: CHỨNG MINH VẤN ĐỀ
+(Prove the Problem)</t>
+        </is>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>Chuẩn hóa kho dữ liệu chính sách, chỉ định Data Owner và đo mốc Baseline W0 trên Jira.</t>
+        </is>
+      </c>
+      <c r="D5" s="51" t="inlineStr">
+        <is>
+          <t>1. 100% tài liệu quy định có chữ ký số Data Owner.
+2. RAG server chặn hoàn toàn câu trả lời không có nguồn.
+3. Xác thực mốc Baseline 42 phút/ca trên Jira.</t>
+        </is>
+      </c>
+      <c r="E5" s="51" t="inlineStr">
+        <is>
+          <t>Head of Data &amp;
+AI Technical Lead</t>
+        </is>
+      </c>
+      <c r="F5" s="51" t="inlineStr">
+        <is>
+          <t>Kéo dài thời gian dọn dẹp dữ liệu thêm 2 tuần; tạm thời chỉ index tập 30 văn bản bồi thường phổ biến nhất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="50" t="inlineStr">
+        <is>
+          <t>31–60 Ngày</t>
+        </is>
+      </c>
+      <c r="B6" s="51" t="inlineStr">
+        <is>
+          <t>CỔNG 2: CHỨNG MINH CHẤT LƯỢNG
+(Prove the Quality)</t>
+        </is>
+      </c>
+      <c r="C6" s="51" t="inlineStr">
+        <is>
+          <t>Vận hành TO-BE workflow trên 30 nhân sự CSKH pilot; kích hoạt nút Báo lỗi 1-click; ban hành chính sách miễn trừ trách nhiệm.</t>
+        </is>
+      </c>
+      <c r="D6" s="51" t="inlineStr">
+        <is>
+          <t>1. Tỷ lệ trích nguồn M04 &gt;= 95%.
+2. Tỷ lệ click kiểm chứng M02 &gt;= 90%.
+3. 0 ca khiếu nại sai chính sách nghiêm trọng.
+4. CSAT nội bộ &gt;= 85%.</t>
+        </is>
+      </c>
+      <c r="E6" s="51" t="inlineStr">
+        <is>
+          <t>Trưởng phòng CSKH &amp;
+QA Lead</t>
+        </is>
+      </c>
+      <c r="F6" s="51" t="inlineStr">
+        <is>
+          <t>Tạm khóa các chuyên mục chính sách có QA pass &lt; 90%; tổ chức kèm cặp 1:1; giữ pilot, không chuyển giai đoạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="50" t="inlineStr">
+        <is>
+          <t>61–90 Ngày</t>
+        </is>
+      </c>
+      <c r="B7" s="51" t="inlineStr">
+        <is>
+          <t>CỔNG 3: QUYẾT ĐỊNH MỞ RỘNG
+(Decide Expansion)</t>
+        </is>
+      </c>
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t>Đo lường năng suất thực tế và ROI kinh tế; Hội đồng Chuyển đổi số họp quyết định Scale hoặc Kill.</t>
+        </is>
+      </c>
+      <c r="D7" s="51" t="inlineStr">
+        <is>
+          <t>1. Cycle time M03 &lt;= 15 phút (giảm &gt;60%).
+2. Tỷ lệ khiếu nại lại M05 &lt;= 1.0%.
+3. Tiết kiệm OPEX M06 &gt; 60%.
+4. COO &amp; Pháp chế ký duyệt an toàn.</t>
+        </is>
+      </c>
+      <c r="E7" s="51" t="inlineStr">
+        <is>
+          <t>Giám đốc Vận hành (COO) &amp;
+Product Owner AI</t>
+        </is>
+      </c>
+      <c r="F7" s="51" t="inlineStr">
+        <is>
+          <t>Nếu không đạt ROI hoặc rủi ro pháp lý còn cao: Tuyên bố dừng (Kill) hoặc duy trì pilot hẹp, không chi ngân sách mở rộng.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>